--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/feb-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/feb-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC feb-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC feb-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/feb-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/feb-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -623,7 +623,11 @@
           <t>76.260.080-3</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>76.093.443-7</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +875,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -941,7 +953,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1725-4419-CM25</t>
+          <t>1314-15-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -961,48 +973,52 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>G-Talent SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>52.004.665-8</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>56941.6</v>
+        <v>18245.26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1314-15-CM25</t>
+          <t>1314-14-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1050,20 +1066,24 @@
           <t>52.004.665-8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>18245.26</v>
+        <v>18235.81</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1314-14-CM25</t>
+          <t>1725-4419-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1083,32 +1103,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>G-Talent SPA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>52.004.665-8</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1138,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>18235.81</v>
+        <v>56941.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1314-13-CM25</t>
+          <t>2147-43-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1144,48 +1164,52 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>61.606.406-1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>G-Talent SPA</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>52.004.665-8</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>76.624.276-6</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>18245.36</v>
+        <v>26993.62</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2147-43-CM25</t>
+          <t>45-23-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1210,27 +1234,27 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Georg</t>
+          <t>RIALIS SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
+          <t>76.348.639-7</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1264,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>26993.62</v>
+        <v>58220.51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>45-23-CM25</t>
+          <t>1314-13-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1266,17 +1290,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,22 +1310,26 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>RIALIS SPA</t>
+          <t>G-Talent SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.348.639-7</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>52.004.665-8</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>58220.51</v>
+        <v>18245.36</v>
       </c>
     </row>
     <row r="15">
@@ -1355,7 +1383,11 @@
           <t>77.077.350-4</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1570,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1696,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1673,7 +1713,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1314-18-CM25</t>
+          <t>4202-5-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1693,17 +1733,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>69.073.900-3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>I MUNICIPALIDAD DE CURACAVI</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,28 +1753,32 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>G-Talent SPA</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>52.004.665-8</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>18488.04</v>
+        <v>21427.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4202-5-CM25</t>
+          <t>2792-758-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1754,17 +1798,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.073.900-3</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAVI</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1818,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Zecovery Ltda   -    EXEC</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1833,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>21427.5</v>
+        <v>42130.36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2792-758-CM25</t>
+          <t>1314-17-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1820,12 +1864,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,28 +1879,32 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>G-Talent SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>52.004.665-8</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>42130.36</v>
+        <v>18488.04</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1314-17-CM25</t>
+          <t>1314-18-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1904,7 +1952,11 @@
           <t>52.004.665-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1917,7 +1969,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1314-19-CM25</t>
+          <t>1230865-5-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1937,17 +1989,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>70.913.100-1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>Corporación Comunal de Desarrollo Quinta Normal</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +2009,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>G-Talent SPA</t>
+          <t>DATCO CHILE S A</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>52.004.665-8</t>
+          <t>96.897.630-3</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +2024,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>18817.18</v>
+        <v>25568.89</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1230865-5-CM25</t>
+          <t>1314-19-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1998,17 +2050,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>70.913.100-1</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Corporación Comunal de Desarrollo Quinta Normal</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,22 +2070,26 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>DATCO CHILE S A</t>
+          <t>G-Talent SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>96.897.630-3</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>52.004.665-8</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>25568.89</v>
+        <v>18817.18</v>
       </c>
     </row>
     <row r="27">
@@ -2148,7 +2204,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2574,11 @@
           <t>52.004.665-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2527,7 +2591,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1602-23-CM25</t>
+          <t>45-49-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2552,12 +2616,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,28 +2631,32 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>VAB Ingeniería de Software Limitada</t>
+          <t>Fernando Marcelo</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.090.261-6</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>76.811.563-K</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>24911.94</v>
+        <v>6899.86</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1057554-59-CM25</t>
+          <t>1602-23-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2608,32 +2676,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Georg</t>
+          <t>VAB Ingeniería de Software Limitada</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
+          <t>76.090.261-6</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,7 +2711,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>55331.01</v>
+        <v>24911.94</v>
       </c>
     </row>
     <row r="37">
@@ -2697,7 +2765,11 @@
           <t>76.188.587-1</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2710,7 +2782,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>45-49-CM25</t>
+          <t>1057554-59-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2730,42 +2802,46 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Fernando Marcelo</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.811.563-K</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>76.624.276-6</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>6899.86</v>
+        <v>55331.01</v>
       </c>
     </row>
     <row r="39">
@@ -3002,7 +3078,11 @@
           <t>76.624.276-6</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3198,7 +3278,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>14-59-CM25</t>
+          <t>957865-85-SE25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3223,12 +3303,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.980.820-7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>SUBSECRETARIA DE DERECHOS HUMANOS</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,28 +3318,32 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.454.923-6</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>14292.63</v>
+        <v>61550.02</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2799-193-CM25</t>
+          <t>14-59-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3284,27 +3368,27 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SolNet SPA</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>76.454.923-6</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,6 +3398,67 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
+        <v>14292.63</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2799-193-CM25</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>feb-2025</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>69.051.100-2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>SolNet SPA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>96.723.130-4</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
         <v>28861.46</v>
       </c>
     </row>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/feb-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/feb-2025.xlsx
@@ -1131,7 +1131,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2269,7 +2273,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
